--- a/dataset/Faulty/invalid_memory_access.xlsx
+++ b/dataset/Faulty/invalid_memory_access.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -588,14 +588,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -610,14 +610,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,19 +627,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>typedef union { int *a; int b; } invalid_memory_access_009_s_001; typedef struct { invalid_memory_access_009_s_001 *s1; invalid_memory_access_009_s_002 s2; invalid_memory_access_009_s_003 s3; } invalid_memory_access_009_uni_001; char ** invalid_memory_access_016_doubleptr_gbl; char *invalid_memory_access_017_doubleptr_gbl; static int staticflag1=1; invalid_memory_access_013_s_001 *invalid_memory_access_013_s_001_s_gbl; extern volatile int vflag; void invalid_memory_access_009 () { invalid_memory_access_009_uni_001 *u = (invalid_memory_access_009_uni_001 * )malloc(5*sizeof( invalid_memory_access_009_uni_001 )); invalid_memory_access_009_uni_001 *p = NULL; if(u!=NULL) { u-&gt;s1 = (invalid_memory_access_009_s_001 *) malloc(sizeof(invalid_memory_access_009_s_001)); if(u-&gt;s1!=NULL) u-&gt;s1-&gt;a = (int *) malloc(5*sizeof(int)); p = u; p-&gt;s1-&gt;a[0] = 1; free(u-&gt;s1-&gt;a); free(u-&gt;s1); free(u); p-&gt;s1-&gt;a[0] = 1; /*Tool should detect this line as error*/ /*ERROR:Invalid memory access to already freed area*/ } }</t>
+          <t>typedef struct { invalid_memory_access_009_s_001 *s1; invalid_memory_access_009_s_002 s2; invalid_memory_access_009_s_003 s3; } invalid_memory_access_009_uni_001; typedef union { int *a; int b; } invalid_memory_access_009_s_001; char ** invalid_memory_access_016_doubleptr_gbl; char *invalid_memory_access_017_doubleptr_gbl; static int staticflag1=1; invalid_memory_access_013_s_001 *invalid_memory_access_013_s_001_s_gbl; extern volatile int vflag; void invalid_memory_access_009 () { invalid_memory_access_009_uni_001 *u = (invalid_memory_access_009_uni_001 * )malloc(5*sizeof( invalid_memory_access_009_uni_001 )); invalid_memory_access_009_uni_001 *p = NULL; if(u!=NULL) { u-&gt;s1 = (invalid_memory_access_009_s_001 *) malloc(sizeof(invalid_memory_access_009_s_001)); if(u-&gt;s1!=NULL) u-&gt;s1-&gt;a = (int *) malloc(5*sizeof(int)); p = u; p-&gt;s1-&gt;a[0] = 1; free(u-&gt;s1-&gt;a); free(u-&gt;s1); free(u); p-&gt;s1-&gt;a[0] = 1; /*Tool should detect this line as error*/ /*ERROR:Invalid memory access to already freed area*/ } }</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -654,14 +654,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -676,14 +676,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>typedef struct { int a; int b; int uninit; } invalid_memory_access_013_s_001; char ** invalid_memory_access_016_doubleptr_gbl; char *invalid_memory_access_017_doubleptr_gbl; static int staticflag1=1; invalid_memory_access_013_s_001 *invalid_memory_access_013_s_001_s_gbl; extern volatile int vflag; void invalid_memory_access_013 () { int ret; invalid_memory_access_013_func_001 (1); ret = invalid_memory_access_013_func_002 (1); invalid_memory_access_013_func_003 (0); printf("%d",ret); } void invalid_memory_access_013_func_001 (int flag) { if(flag &gt;0) invalid_memory_access_013_s_001_s_gbl = (invalid_memory_access_013_s_001 *)calloc(1,sizeof(invalid_memory_access_013_s_001)); } int invalid_memory_access_013_func_002 (int flag) { int i=0; switch (flag) { case 1: { if (invalid_memory_access_013_s_001_s_gbl != NULL) { invalid_memory_access_013_s_001_s_gbl-&gt;a = 10; invalid_memory_access_013_s_001_s_gbl-&gt;b = 10; invalid_memory_access_013_s_001_s_gbl-&gt;uninit = 10; i=invalid_memory_access_013_s_001_s_gbl-&gt;a; free(invalid_memory_access_013_s_001_s_gbl); } break; } case 2: { if (invalid_memory_access_013_s_001_s_gbl != NULL) { invalid_memory_access_013_s_001_s_gbl-&gt;a = 20; invalid_memory_access_013_s_001_s_gbl-&gt;b = 20; invalid_memory_access_013_s_001_s_gbl-&gt;uninit = 20; i=invalid_memory_access_013_s_001_s_gbl-&gt;a; free(invalid_memory_access_013_s_001_s_gbl); } break; } default: { break; } } return invalid_memory_access_013_s_001_s_gbl-&gt;a;/*Tool should detect this line as error*/ /*ERROR:Invalid memory access to already freed area*/ } void invalid_memory_access_013_func_003 (int flag) { invalid_memory_access_013_s_001 s; if(flag &gt;0) { if (invalid_memory_access_013_s_001_s_gbl != NULL) { s.a = invalid_memory_access_013_s_001_s_gbl-&gt;a; s.b = invalid_memory_access_013_s_001_s_gbl-&gt;b; s.uninit = invalid_memory_access_013_s_001_s_gbl-&gt;uninit; } } }</t>
+          <t>typedef struct { int a; int b; int uninit; } invalid_memory_access_013_s_001; char ** invalid_memory_access_016_doubleptr_gbl; char *invalid_memory_access_017_doubleptr_gbl; static int staticflag1=1; invalid_memory_access_013_s_001 *invalid_memory_access_013_s_001_s_gbl; extern volatile int vflag; void invalid_memory_access_013 () { int ret; invalid_memory_access_013_func_001 (1); ret = invalid_memory_access_013_func_002 (1); invalid_memory_access_013_func_003 (0); printf("%d",ret); } int invalid_memory_access_013_func_002 (int flag) { int i=0; switch (flag) { case 1: { if (invalid_memory_access_013_s_001_s_gbl != NULL) { invalid_memory_access_013_s_001_s_gbl-&gt;a = 10; invalid_memory_access_013_s_001_s_gbl-&gt;b = 10; invalid_memory_access_013_s_001_s_gbl-&gt;uninit = 10; i=invalid_memory_access_013_s_001_s_gbl-&gt;a; free(invalid_memory_access_013_s_001_s_gbl); } break; } case 2: { if (invalid_memory_access_013_s_001_s_gbl != NULL) { invalid_memory_access_013_s_001_s_gbl-&gt;a = 20; invalid_memory_access_013_s_001_s_gbl-&gt;b = 20; invalid_memory_access_013_s_001_s_gbl-&gt;uninit = 20; i=invalid_memory_access_013_s_001_s_gbl-&gt;a; free(invalid_memory_access_013_s_001_s_gbl); } break; } default: { break; } } return invalid_memory_access_013_s_001_s_gbl-&gt;a;/*Tool should detect this line as error*/ /*ERROR:Invalid memory access to already freed area*/ } void invalid_memory_access_013_func_003 (int flag) { invalid_memory_access_013_s_001 s; if(flag &gt;0) { if (invalid_memory_access_013_s_001_s_gbl != NULL) { s.a = invalid_memory_access_013_s_001_s_gbl-&gt;a; s.b = invalid_memory_access_013_s_001_s_gbl-&gt;b; s.uninit = invalid_memory_access_013_s_001_s_gbl-&gt;uninit; } } } void invalid_memory_access_013_func_001 (int flag) { if(flag &gt;0) invalid_memory_access_013_s_001_s_gbl = (invalid_memory_access_013_s_001 *)calloc(1,sizeof(invalid_memory_access_013_s_001)); }</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -764,14 +764,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -786,14 +786,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/invalid_memory_access.c</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>char ** invalid_memory_access_016_doubleptr_gbl; char *invalid_memory_access_017_doubleptr_gbl; static int staticflag1=1; invalid_memory_access_013_s_001 *invalid_memory_access_013_s_001_s_gbl; extern volatile int vflag; void invalid_memory_access_017() { int flag=10; if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_002(); } if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_003(); } if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_004(); } } void invalid_memory_access_017_func_004() { char s[10] ; strcpy(s,invalid_memory_access_017_doubleptr_gbl);/*Tool should detect this line as error*/ /*ERROR:Invalid memory access to already freed area*/ } void invalid_memory_access_017_func_003() { free(invalid_memory_access_017_doubleptr_gbl); } void invalid_memory_access_017_func_002() { invalid_memory_access_017_doubleptr_gbl=(char*) malloc(10*sizeof(char)); if(invalid_memory_access_017_doubleptr_gbl !=NULL) strcpy(invalid_memory_access_017_doubleptr_gbl,"TEST"); } int invalid_memory_access_017_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; }</t>
+          <t>char ** invalid_memory_access_016_doubleptr_gbl; char *invalid_memory_access_017_doubleptr_gbl; static int staticflag1=1; invalid_memory_access_013_s_001 *invalid_memory_access_013_s_001_s_gbl; extern volatile int vflag; void invalid_memory_access_017() { int flag=10; if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_002(); } if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_003(); } if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_004(); } } void invalid_memory_access_017_func_003() { free(invalid_memory_access_017_doubleptr_gbl); } int invalid_memory_access_017_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; } void invalid_memory_access_017_func_002() { invalid_memory_access_017_doubleptr_gbl=(char*) malloc(10*sizeof(char)); if(invalid_memory_access_017_doubleptr_gbl !=NULL) strcpy(invalid_memory_access_017_doubleptr_gbl,"TEST"); } void invalid_memory_access_017_func_004() { char s[10] ; strcpy(s,invalid_memory_access_017_doubleptr_gbl);/*Tool should detect this line as error*/ /*ERROR:Invalid memory access to already freed area*/ }</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
